--- a/volunteer_forms/009_youth_volunteer_engagement_feedback_evaluation_form--volunteer_forms.xlsx
+++ b/volunteer_forms/009_youth_volunteer_engagement_feedback_evaluation_form--volunteer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>program_outcome</t>
+          <t>program_outcome_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>program_outcome</t>
+          <t>program_outcome_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>program_outcome</t>
+          <t>program_outcome_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>program_outcome</t>
+          <t>program_outcome_5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>program_outcome</t>
+          <t>program_outcome_6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>volunteer_feedback</t>
+          <t>volunteer_feedback_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>program_outcome</t>
+          <t>program_outcome_7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Volunteer feedback</t>
+          <t>Program Outcome 7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>program_outcome</t>
+          <t>program_outcome_8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>program_outcome</t>
+          <t>program_outcome_9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>volunteer_outcomes</t>
+          <t>volunteer_outcomes_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Volunteer outcomes</t>
+          <t>Volunteer Outcomes 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>program_outcome</t>
+          <t>program_outcome_10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>program_outcome</t>
+          <t>program_outcome_11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>volunteer suggestions</t>
+          <t>volunteer suggestions (2)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>volunteer_comments</t>
+          <t>volunteer_comments_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>volunteer comments</t>
+          <t>Volunteer Comments 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>program_outcome</t>
+          <t>program_outcome_12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>program outcomes</t>
+          <t>Program Outcome 12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>volunteer outcomes</t>
+          <t>Volunteer Outcome</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>volunteer_outcome</t>
+          <t>volunteer_outcome_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>program outcomes</t>
+          <t>Volunteer Outcome 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>volunteer_outcome</t>
+          <t>volunteer_outcome_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>outcome</t>
+          <t>Volunteer Outcome 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>program_outcome</t>
+          <t>program_outcome_13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Program Outcome</t>
+          <t>Program Outcome 13</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1194,7 +1194,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>program_outcome_choices</t>
+          <t>program_outcome_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>program_outcome_choices</t>
+          <t>program_outcome_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>program_outcome_choices</t>
+          <t>program_outcome_4_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>program_outcome_choices</t>
+          <t>program_outcome_4_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>program_outcome_choices</t>
+          <t>program_outcome_4_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
